--- a/output/pdf_financials_xlsx/GHL.xlsx
+++ b/output/pdf_financials_xlsx/GHL.xlsx
@@ -5944,31 +5944,31 @@
         <v>1.670478</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.872478</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.872478</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.872478</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.015003</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.876808</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.843056</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.843056</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.843056</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.843056</v>
       </c>
     </row>
     <row r="93">
@@ -9597,7 +9597,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10179,7 +10183,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10975,7 +10983,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11894,7 +11906,11 @@
           <t>Share based payment reserve 12</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GHL.xlsx
+++ b/output/pdf_financials_xlsx/GHL.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005092</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1053,13 +1053,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002997</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.003677</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000841</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.414824</v>
+        <v>-2.419916</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.6652749999999999</v>
@@ -2001,13 +2001,13 @@
         <v>-0.45972</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.882745</v>
+        <v>-0.885742</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.880104</v>
+        <v>-0.883781</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.552341</v>
+        <v>-0.553182</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.420838</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.414824</v>
+        <v>-2.419916</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.6652749999999999</v>
@@ -2117,13 +2117,13 @@
         <v>-0.45972</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.882745</v>
+        <v>-0.885742</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.880104</v>
+        <v>-0.883781</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.552341</v>
+        <v>-0.553182</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.420838</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09080299999999999</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.004922</v>
@@ -2430,25 +2430,25 @@
         <v>0.087559</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06135</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.036455</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.167473</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.046014</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.035889</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.171584</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.028804</v>
       </c>
     </row>
     <row r="35">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09080299999999999</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.004922</v>
@@ -2546,25 +2546,25 @@
         <v>0.087559</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06135</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.036455</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.167473</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.046014</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.035889</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.171584</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.028804</v>
       </c>
     </row>
     <row r="37">
@@ -3221,13 +3221,13 @@
         <v>0.111136</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.006816</v>
+        <v>0.015226</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.006763</v>
+        <v>0.015617</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.006529</v>
+        <v>0.007466</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.014012</v>
@@ -3242,25 +3242,25 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.06135</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.036818</v>
+        <v>0.000363</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.176866</v>
+        <v>0.009393</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.096011</v>
+        <v>0.049997</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.037876</v>
+        <v>0.001987</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.172831</v>
+        <v>0.001247</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.030054</v>
+        <v>0.00125</v>
       </c>
     </row>
     <row r="49">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -39656,7 +39656,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E326" s="5" t="n">

--- a/output/pdf_financials_xlsx/GHL.xlsx
+++ b/output/pdf_financials_xlsx/GHL.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.07378</v>
+        <v>0.30602</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.020801</v>
+        <v>0.07387299999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.291945</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.075032</v>
+        <v>0.307272</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.023123</v>
+        <v>0.076195</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.419824</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>5.496775</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>5.677255</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>0</v>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.679801</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.057711</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -17413,7 +17413,11 @@
           <t>Due to related party – Note 5</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -17514,7 +17518,11 @@
           <t>Share capital – Notes 6 and 12</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>5.496775</v>
       </c>
@@ -17714,7 +17722,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.679801</v>
       </c>
@@ -49164,7 +49176,11 @@
           <t>Management fees – Note 5</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
         <v>0.23224</v>
       </c>
@@ -49362,7 +49378,11 @@
           <t>Professional fees – Note 5</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E409" s="5" t="n">
         <v>0.049697</v>
       </c>

--- a/output/pdf_financials_xlsx/GHL.xlsx
+++ b/output/pdf_financials_xlsx/GHL.xlsx
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.001252</v>
+        <v>0.021004</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.002322</v>
+        <v>0.008621999999999999</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.127879</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.307272</v>
+        <v>0.327024</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.076195</v>
+        <v>0.082495</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.419824</v>
@@ -49679,7 +49679,11 @@
           <t>Rent and occupancy costs – Note 5</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E412" s="5" t="n">
         <v>0.019752</v>
       </c>

--- a/output/pdf_financials_xlsx/GHL.xlsx
+++ b/output/pdf_financials_xlsx/GHL.xlsx
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.013002</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.003589</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -7185,13 +7185,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.00364</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.063154</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -19215,7 +19215,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -23078,7 +23082,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23179,7 +23187,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -24462,7 +24474,11 @@
           <t>Acquisition of investments 7</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -24965,7 +24981,11 @@
           <t>Shares issued for cash 12</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -30445,7 +30465,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>0.013002</v>
       </c>
